--- a/artfynd/A 32048-2025 artfynd.xlsx
+++ b/artfynd/A 32048-2025 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126600450</v>
+        <v>126600435</v>
       </c>
       <c r="B2" t="n">
-        <v>56849</v>
+        <v>79629</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Öjvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>408342</v>
+        <v>408398</v>
       </c>
       <c r="R2" t="n">
-        <v>6857500</v>
+        <v>6857513</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126600435</v>
+        <v>126600529</v>
       </c>
       <c r="B3" t="n">
-        <v>79598</v>
+        <v>79011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>408398</v>
+        <v>407761</v>
       </c>
       <c r="R3" t="n">
-        <v>6857513</v>
+        <v>6857385</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,45 +869,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126600529</v>
+        <v>126600450</v>
       </c>
       <c r="B4" t="n">
-        <v>78980</v>
+        <v>56849</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Öjvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>407761</v>
+        <v>408342</v>
       </c>
       <c r="R4" t="n">
-        <v>6857385</v>
+        <v>6857500</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
         <v>126600490</v>
       </c>
       <c r="B5" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>126600530</v>
       </c>
       <c r="B6" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126600452</v>
+        <v>126600468</v>
       </c>
       <c r="B7" t="n">
-        <v>57817</v>
+        <v>79011</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>408326</v>
+        <v>407930</v>
       </c>
       <c r="R7" t="n">
-        <v>6857475</v>
+        <v>6857464</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1236,6 +1236,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På minst 250 å gammal tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1262,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126600468</v>
+        <v>126600452</v>
       </c>
       <c r="B8" t="n">
-        <v>78980</v>
+        <v>57817</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>407930</v>
+        <v>408326</v>
       </c>
       <c r="R8" t="n">
-        <v>6857464</v>
+        <v>6857475</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1333,11 +1338,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-11</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På minst 250 å gammal tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126600473</v>
+        <v>126600478</v>
       </c>
       <c r="B9" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>407787</v>
+        <v>407856</v>
       </c>
       <c r="R9" t="n">
-        <v>6857454</v>
+        <v>6857458</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126600515</v>
+        <v>126600467</v>
       </c>
       <c r="B10" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>408515</v>
+        <v>408188</v>
       </c>
       <c r="R10" t="n">
-        <v>6857517</v>
+        <v>6857426</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1532,6 +1532,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På minst 300 å gammal tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1561,7 +1566,7 @@
         <v>126600486</v>
       </c>
       <c r="B11" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1655,10 +1660,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126600478</v>
+        <v>126600473</v>
       </c>
       <c r="B12" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1690,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>407856</v>
+        <v>407787</v>
       </c>
       <c r="R12" t="n">
-        <v>6857458</v>
+        <v>6857454</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1752,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126600467</v>
+        <v>126600515</v>
       </c>
       <c r="B13" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1787,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>408188</v>
+        <v>408515</v>
       </c>
       <c r="R13" t="n">
-        <v>6857426</v>
+        <v>6857517</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1823,11 +1828,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-11</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På minst 300 å gammal tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1854,10 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126600481</v>
+        <v>126600434</v>
       </c>
       <c r="B14" t="n">
-        <v>78980</v>
+        <v>79629</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1865,21 +1865,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>407943</v>
+        <v>408371</v>
       </c>
       <c r="R14" t="n">
-        <v>6857431</v>
+        <v>6857511</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1954,7 +1954,7 @@
         <v>126600519</v>
       </c>
       <c r="B15" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2048,10 +2048,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126600434</v>
+        <v>126600481</v>
       </c>
       <c r="B16" t="n">
-        <v>79598</v>
+        <v>79011</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2059,21 +2059,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2083,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>408371</v>
+        <v>407943</v>
       </c>
       <c r="R16" t="n">
-        <v>6857511</v>
+        <v>6857431</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2148,7 +2148,7 @@
         <v>126600521</v>
       </c>
       <c r="B17" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>126600509</v>
       </c>
       <c r="B18" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>126600512</v>
       </c>
       <c r="B19" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>126600441</v>
       </c>
       <c r="B20" t="n">
-        <v>75075</v>
+        <v>75135</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>126600489</v>
       </c>
       <c r="B21" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2630,10 +2630,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126600516</v>
+        <v>126600518</v>
       </c>
       <c r="B22" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>408508</v>
+        <v>408503</v>
       </c>
       <c r="R22" t="n">
-        <v>6857524</v>
+        <v>6857520</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2727,10 +2727,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126600518</v>
+        <v>126600477</v>
       </c>
       <c r="B23" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2762,10 +2762,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>408503</v>
+        <v>407841</v>
       </c>
       <c r="R23" t="n">
-        <v>6857520</v>
+        <v>6857451</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2824,10 +2824,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126600477</v>
+        <v>126600516</v>
       </c>
       <c r="B24" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>407841</v>
+        <v>408508</v>
       </c>
       <c r="R24" t="n">
-        <v>6857451</v>
+        <v>6857524</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2921,10 +2921,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126600447</v>
+        <v>126600507</v>
       </c>
       <c r="B25" t="n">
-        <v>79569</v>
+        <v>79011</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2932,21 +2932,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2956,10 +2956,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>408000</v>
+        <v>408520</v>
       </c>
       <c r="R25" t="n">
-        <v>6857426</v>
+        <v>6857470</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -2992,11 +2992,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-11</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>på kulturved</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3023,10 +3018,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126600453</v>
+        <v>126600487</v>
       </c>
       <c r="B26" t="n">
-        <v>57654</v>
+        <v>79011</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3034,39 +3029,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Öjvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>408455</v>
+        <v>408513</v>
       </c>
       <c r="R26" t="n">
-        <v>6857481</v>
+        <v>6857559</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3125,10 +3115,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126600507</v>
+        <v>126600453</v>
       </c>
       <c r="B27" t="n">
-        <v>78980</v>
+        <v>57654</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3136,34 +3126,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Öjvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>408520</v>
+        <v>408455</v>
       </c>
       <c r="R27" t="n">
-        <v>6857470</v>
+        <v>6857481</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3222,10 +3217,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126600487</v>
+        <v>126600447</v>
       </c>
       <c r="B28" t="n">
-        <v>78980</v>
+        <v>79600</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3233,21 +3228,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3257,10 +3252,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>408513</v>
+        <v>408000</v>
       </c>
       <c r="R28" t="n">
-        <v>6857559</v>
+        <v>6857426</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3293,6 +3288,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>på kulturved</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3319,10 +3319,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126600522</v>
+        <v>126600465</v>
       </c>
       <c r="B29" t="n">
-        <v>78980</v>
+        <v>78770</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3330,21 +3330,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3354,10 +3354,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>408161</v>
+        <v>408117</v>
       </c>
       <c r="R29" t="n">
-        <v>6857473</v>
+        <v>6857480</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3416,10 +3416,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126600465</v>
+        <v>126600522</v>
       </c>
       <c r="B30" t="n">
-        <v>78739</v>
+        <v>79011</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3427,21 +3427,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3451,10 +3451,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>408117</v>
+        <v>408161</v>
       </c>
       <c r="R30" t="n">
-        <v>6857480</v>
+        <v>6857473</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3513,10 +3513,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126600483</v>
+        <v>126600475</v>
       </c>
       <c r="B31" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3548,10 +3548,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>408112</v>
+        <v>407812</v>
       </c>
       <c r="R31" t="n">
-        <v>6857501</v>
+        <v>6857450</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3613,7 +3613,7 @@
         <v>126600511</v>
       </c>
       <c r="B32" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         <v>126600488</v>
       </c>
       <c r="B33" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3804,10 +3804,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126600485</v>
+        <v>126600483</v>
       </c>
       <c r="B34" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3839,10 +3839,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>408202</v>
+        <v>408112</v>
       </c>
       <c r="R34" t="n">
-        <v>6857508</v>
+        <v>6857501</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3901,10 +3901,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126600475</v>
+        <v>126600485</v>
       </c>
       <c r="B35" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3936,10 +3936,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>407812</v>
+        <v>408202</v>
       </c>
       <c r="R35" t="n">
-        <v>6857450</v>
+        <v>6857508</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3998,10 +3998,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126600445</v>
+        <v>126600517</v>
       </c>
       <c r="B36" t="n">
-        <v>75075</v>
+        <v>79011</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4009,21 +4009,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4033,10 +4033,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>407749</v>
+        <v>408506</v>
       </c>
       <c r="R36" t="n">
-        <v>6857376</v>
+        <v>6857522</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4095,10 +4095,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126600505</v>
+        <v>126600514</v>
       </c>
       <c r="B37" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4130,10 +4130,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>408526</v>
+        <v>408519</v>
       </c>
       <c r="R37" t="n">
-        <v>6857470</v>
+        <v>6857527</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4192,10 +4192,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126600517</v>
+        <v>126600531</v>
       </c>
       <c r="B38" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4227,10 +4227,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>408506</v>
+        <v>407732</v>
       </c>
       <c r="R38" t="n">
-        <v>6857522</v>
+        <v>6857407</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4289,10 +4289,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126600531</v>
+        <v>126600505</v>
       </c>
       <c r="B39" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4324,10 +4324,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>407732</v>
+        <v>408526</v>
       </c>
       <c r="R39" t="n">
-        <v>6857407</v>
+        <v>6857470</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4386,10 +4386,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126600514</v>
+        <v>126600445</v>
       </c>
       <c r="B40" t="n">
-        <v>78980</v>
+        <v>75135</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4397,21 +4397,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4421,10 +4421,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>408519</v>
+        <v>407749</v>
       </c>
       <c r="R40" t="n">
-        <v>6857527</v>
+        <v>6857376</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4486,7 +4486,7 @@
         <v>126600484</v>
       </c>
       <c r="B41" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4580,10 +4580,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126600533</v>
+        <v>126600527</v>
       </c>
       <c r="B42" t="n">
-        <v>88654</v>
+        <v>79011</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4591,21 +4591,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4615,13 +4615,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>408505</v>
+        <v>407828</v>
       </c>
       <c r="R42" t="n">
-        <v>6857526</v>
+        <v>6857402</v>
       </c>
       <c r="S42" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4677,10 +4677,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126600527</v>
+        <v>126600525</v>
       </c>
       <c r="B43" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4712,10 +4712,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>407828</v>
+        <v>407847</v>
       </c>
       <c r="R43" t="n">
-        <v>6857402</v>
+        <v>6857413</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4774,10 +4774,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126600525</v>
+        <v>126600533</v>
       </c>
       <c r="B44" t="n">
-        <v>78980</v>
+        <v>88722</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4785,21 +4785,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4809,13 +4809,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>407847</v>
+        <v>408505</v>
       </c>
       <c r="R44" t="n">
-        <v>6857413</v>
+        <v>6857526</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4973,10 +4973,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126600438</v>
+        <v>126600439</v>
       </c>
       <c r="B46" t="n">
-        <v>79598</v>
+        <v>75135</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4984,21 +4984,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5008,10 +5008,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>408116</v>
+        <v>408539</v>
       </c>
       <c r="R46" t="n">
-        <v>6857480</v>
+        <v>6857475</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5044,6 +5044,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>rikligt, på minst 300 år gammal gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5070,10 +5075,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126600508</v>
+        <v>126600438</v>
       </c>
       <c r="B47" t="n">
-        <v>78980</v>
+        <v>79629</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5081,21 +5086,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5105,10 +5110,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>408528</v>
+        <v>408116</v>
       </c>
       <c r="R47" t="n">
-        <v>6857478</v>
+        <v>6857480</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5167,10 +5172,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126600439</v>
+        <v>126600508</v>
       </c>
       <c r="B48" t="n">
-        <v>75075</v>
+        <v>79011</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5178,21 +5183,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5202,10 +5207,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>408539</v>
+        <v>408528</v>
       </c>
       <c r="R48" t="n">
-        <v>6857475</v>
+        <v>6857478</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5238,11 +5243,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-07-11</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>rikligt, på minst 300 år gammal gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5269,10 +5269,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126600528</v>
+        <v>126600444</v>
       </c>
       <c r="B49" t="n">
-        <v>78980</v>
+        <v>75135</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5280,21 +5280,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5304,10 +5304,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>407819</v>
+        <v>407771</v>
       </c>
       <c r="R49" t="n">
-        <v>6857401</v>
+        <v>6857396</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5366,10 +5366,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126600482</v>
+        <v>126600528</v>
       </c>
       <c r="B50" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5401,10 +5401,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>407948</v>
+        <v>407819</v>
       </c>
       <c r="R50" t="n">
-        <v>6857423</v>
+        <v>6857401</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5463,10 +5463,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126600444</v>
+        <v>126600482</v>
       </c>
       <c r="B51" t="n">
-        <v>75075</v>
+        <v>79011</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5474,21 +5474,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5498,10 +5498,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>407771</v>
+        <v>407948</v>
       </c>
       <c r="R51" t="n">
-        <v>6857396</v>
+        <v>6857423</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5667,10 +5667,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126600474</v>
+        <v>126600470</v>
       </c>
       <c r="B53" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5702,10 +5702,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>407795</v>
+        <v>408475</v>
       </c>
       <c r="R53" t="n">
-        <v>6857454</v>
+        <v>6857511</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5738,6 +5738,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>På minst 200 år gammal gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5764,10 +5769,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126600470</v>
+        <v>126600474</v>
       </c>
       <c r="B54" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5799,10 +5804,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>408475</v>
+        <v>407795</v>
       </c>
       <c r="R54" t="n">
-        <v>6857511</v>
+        <v>6857454</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5835,11 +5840,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-07-11</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>På minst 200 år gammal gran</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5866,10 +5866,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126600532</v>
+        <v>126600480</v>
       </c>
       <c r="B55" t="n">
-        <v>57657</v>
+        <v>79011</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5877,39 +5877,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Öjvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>408545</v>
+        <v>407893</v>
       </c>
       <c r="R55" t="n">
-        <v>6857481</v>
+        <v>6857487</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5968,10 +5963,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126600480</v>
+        <v>126600532</v>
       </c>
       <c r="B56" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5979,34 +5974,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Öjvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>407893</v>
+        <v>408545</v>
       </c>
       <c r="R56" t="n">
-        <v>6857487</v>
+        <v>6857481</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6065,10 +6065,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126600443</v>
+        <v>126600523</v>
       </c>
       <c r="B57" t="n">
-        <v>75075</v>
+        <v>79011</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6076,21 +6076,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6100,10 +6100,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>408515</v>
+        <v>407896</v>
       </c>
       <c r="R57" t="n">
-        <v>6857485</v>
+        <v>6857412</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6162,10 +6162,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126600436</v>
+        <v>126600443</v>
       </c>
       <c r="B58" t="n">
-        <v>79598</v>
+        <v>75135</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6173,21 +6173,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6197,10 +6197,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>408460</v>
+        <v>408515</v>
       </c>
       <c r="R58" t="n">
-        <v>6857480</v>
+        <v>6857485</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6259,10 +6259,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126600523</v>
+        <v>126600476</v>
       </c>
       <c r="B59" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6294,10 +6294,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>407896</v>
+        <v>407830</v>
       </c>
       <c r="R59" t="n">
-        <v>6857412</v>
+        <v>6857446</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6356,10 +6356,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126600476</v>
+        <v>126600436</v>
       </c>
       <c r="B60" t="n">
-        <v>78980</v>
+        <v>79629</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6367,21 +6367,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6391,10 +6391,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>407830</v>
+        <v>408460</v>
       </c>
       <c r="R60" t="n">
-        <v>6857446</v>
+        <v>6857480</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6453,10 +6453,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126600466</v>
+        <v>126600469</v>
       </c>
       <c r="B61" t="n">
-        <v>91263</v>
+        <v>79011</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6464,21 +6464,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6488,10 +6488,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>408497</v>
+        <v>408448</v>
       </c>
       <c r="R61" t="n">
-        <v>6857526</v>
+        <v>6857547</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6524,6 +6524,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>På minst 250 å gammal tall</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6550,10 +6555,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126600469</v>
+        <v>126600504</v>
       </c>
       <c r="B62" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6585,10 +6590,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>408448</v>
+        <v>408547</v>
       </c>
       <c r="R62" t="n">
-        <v>6857547</v>
+        <v>6857475</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6621,11 +6626,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-07-11</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>På minst 250 å gammal tall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6652,10 +6652,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126600524</v>
+        <v>126600510</v>
       </c>
       <c r="B63" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6687,10 +6687,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>407853</v>
+        <v>408517</v>
       </c>
       <c r="R63" t="n">
-        <v>6857393</v>
+        <v>6857489</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6749,10 +6749,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126600504</v>
+        <v>126600520</v>
       </c>
       <c r="B64" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6784,10 +6784,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>408547</v>
+        <v>408455</v>
       </c>
       <c r="R64" t="n">
-        <v>6857475</v>
+        <v>6857481</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6846,10 +6846,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126600520</v>
+        <v>126600524</v>
       </c>
       <c r="B65" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6881,10 +6881,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>408455</v>
+        <v>407853</v>
       </c>
       <c r="R65" t="n">
-        <v>6857481</v>
+        <v>6857393</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6943,10 +6943,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126600510</v>
+        <v>126600466</v>
       </c>
       <c r="B66" t="n">
-        <v>78980</v>
+        <v>91337</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6954,21 +6954,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6978,10 +6978,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>408517</v>
+        <v>408497</v>
       </c>
       <c r="R66" t="n">
-        <v>6857489</v>
+        <v>6857526</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7040,10 +7040,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126600437</v>
+        <v>126600471</v>
       </c>
       <c r="B67" t="n">
-        <v>79598</v>
+        <v>79011</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7051,21 +7051,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7075,10 +7075,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>408172</v>
+        <v>408442</v>
       </c>
       <c r="R67" t="n">
-        <v>6857457</v>
+        <v>6857466</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7111,6 +7111,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7137,10 +7142,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126600471</v>
+        <v>126600437</v>
       </c>
       <c r="B68" t="n">
-        <v>78980</v>
+        <v>79629</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7148,21 +7153,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7172,10 +7177,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>408442</v>
+        <v>408172</v>
       </c>
       <c r="R68" t="n">
-        <v>6857466</v>
+        <v>6857457</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7208,11 +7213,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-07-11</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7239,10 +7239,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126600455</v>
+        <v>126600472</v>
       </c>
       <c r="B69" t="n">
-        <v>57657</v>
+        <v>79011</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7250,39 +7250,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Öjvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>408538</v>
+        <v>407754</v>
       </c>
       <c r="R69" t="n">
-        <v>6857478</v>
+        <v>6857403</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7315,11 +7310,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-07-11</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7346,10 +7336,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126600472</v>
+        <v>126600455</v>
       </c>
       <c r="B70" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7357,34 +7347,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Öjvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>407754</v>
+        <v>408538</v>
       </c>
       <c r="R70" t="n">
-        <v>6857403</v>
+        <v>6857478</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7417,6 +7412,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7446,7 +7446,7 @@
         <v>126600440</v>
       </c>
       <c r="B71" t="n">
-        <v>75075</v>
+        <v>75135</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         <v>126600498</v>
       </c>
       <c r="B72" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
         <v>126600492</v>
       </c>
       <c r="B73" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7737,7 +7737,7 @@
         <v>126600503</v>
       </c>
       <c r="B74" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>126600494</v>
       </c>
       <c r="B75" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>126600502</v>
       </c>
       <c r="B76" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8028,7 +8028,7 @@
         <v>126600496</v>
       </c>
       <c r="B77" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         <v>126600493</v>
       </c>
       <c r="B78" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8222,7 +8222,7 @@
         <v>126600491</v>
       </c>
       <c r="B79" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8319,7 +8319,7 @@
         <v>126600442</v>
       </c>
       <c r="B80" t="n">
-        <v>75075</v>
+        <v>75135</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
         <v>126600499</v>
       </c>
       <c r="B82" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8620,7 +8620,7 @@
         <v>126600495</v>
       </c>
       <c r="B83" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 32048-2025 artfynd.xlsx
+++ b/artfynd/A 32048-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126600435</v>
       </c>
       <c r="B2" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126600529</v>
       </c>
       <c r="B3" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>126600490</v>
       </c>
       <c r="B5" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126600530</v>
+        <v>126600452</v>
       </c>
       <c r="B6" t="n">
-        <v>79011</v>
+        <v>57817</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>407733</v>
+        <v>408326</v>
       </c>
       <c r="R6" t="n">
-        <v>6857392</v>
+        <v>6857475</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126600468</v>
+        <v>126600530</v>
       </c>
       <c r="B7" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>407930</v>
+        <v>407733</v>
       </c>
       <c r="R7" t="n">
-        <v>6857464</v>
+        <v>6857392</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1236,11 +1236,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-11</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På minst 250 å gammal tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1267,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126600452</v>
+        <v>126600468</v>
       </c>
       <c r="B8" t="n">
-        <v>57817</v>
+        <v>79014</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>408326</v>
+        <v>407930</v>
       </c>
       <c r="R8" t="n">
-        <v>6857475</v>
+        <v>6857464</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1338,6 +1333,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På minst 250 å gammal tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1367,7 +1367,7 @@
         <v>126600478</v>
       </c>
       <c r="B9" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>126600467</v>
       </c>
       <c r="B10" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>126600486</v>
       </c>
       <c r="B11" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>126600473</v>
       </c>
       <c r="B12" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>126600515</v>
       </c>
       <c r="B13" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>126600434</v>
       </c>
       <c r="B14" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>126600519</v>
       </c>
       <c r="B15" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         <v>126600481</v>
       </c>
       <c r="B16" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>126600521</v>
       </c>
       <c r="B17" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>126600509</v>
       </c>
       <c r="B18" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>126600512</v>
       </c>
       <c r="B19" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>126600441</v>
       </c>
       <c r="B20" t="n">
-        <v>75135</v>
+        <v>75138</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>126600489</v>
       </c>
       <c r="B21" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>126600518</v>
       </c>
       <c r="B22" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>126600477</v>
       </c>
       <c r="B23" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>126600516</v>
       </c>
       <c r="B24" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2921,10 +2921,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126600507</v>
+        <v>126600453</v>
       </c>
       <c r="B25" t="n">
-        <v>79011</v>
+        <v>57654</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2932,34 +2932,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Öjvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>408520</v>
+        <v>408455</v>
       </c>
       <c r="R25" t="n">
-        <v>6857470</v>
+        <v>6857481</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3018,10 +3023,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126600487</v>
+        <v>126600507</v>
       </c>
       <c r="B26" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3053,10 +3058,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>408513</v>
+        <v>408520</v>
       </c>
       <c r="R26" t="n">
-        <v>6857559</v>
+        <v>6857470</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3115,10 +3120,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126600453</v>
+        <v>126600487</v>
       </c>
       <c r="B27" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3126,39 +3131,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Öjvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>408455</v>
+        <v>408513</v>
       </c>
       <c r="R27" t="n">
-        <v>6857481</v>
+        <v>6857559</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3220,7 +3220,7 @@
         <v>126600447</v>
       </c>
       <c r="B28" t="n">
-        <v>79600</v>
+        <v>79603</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3319,10 +3319,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126600465</v>
+        <v>126600522</v>
       </c>
       <c r="B29" t="n">
-        <v>78770</v>
+        <v>79014</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3330,21 +3330,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3354,10 +3354,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>408117</v>
+        <v>408161</v>
       </c>
       <c r="R29" t="n">
-        <v>6857480</v>
+        <v>6857473</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3416,10 +3416,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126600522</v>
+        <v>126600465</v>
       </c>
       <c r="B30" t="n">
-        <v>79011</v>
+        <v>78773</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3427,21 +3427,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3451,10 +3451,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>408161</v>
+        <v>408117</v>
       </c>
       <c r="R30" t="n">
-        <v>6857473</v>
+        <v>6857480</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3516,7 +3516,7 @@
         <v>126600475</v>
       </c>
       <c r="B31" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3613,7 +3613,7 @@
         <v>126600511</v>
       </c>
       <c r="B32" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         <v>126600488</v>
       </c>
       <c r="B33" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>126600483</v>
       </c>
       <c r="B34" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>126600485</v>
       </c>
       <c r="B35" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>126600517</v>
       </c>
       <c r="B36" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>126600514</v>
       </c>
       <c r="B37" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         <v>126600531</v>
       </c>
       <c r="B38" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         <v>126600505</v>
       </c>
       <c r="B39" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>126600445</v>
       </c>
       <c r="B40" t="n">
-        <v>75135</v>
+        <v>75138</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4486,7 +4486,7 @@
         <v>126600484</v>
       </c>
       <c r="B41" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4583,7 +4583,7 @@
         <v>126600527</v>
       </c>
       <c r="B42" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         <v>126600525</v>
       </c>
       <c r="B43" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4777,7 +4777,7 @@
         <v>126600533</v>
       </c>
       <c r="B44" t="n">
-        <v>88722</v>
+        <v>88728</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         <v>126600439</v>
       </c>
       <c r="B46" t="n">
-        <v>75135</v>
+        <v>75138</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>126600438</v>
       </c>
       <c r="B47" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>126600508</v>
       </c>
       <c r="B48" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>126600444</v>
       </c>
       <c r="B49" t="n">
-        <v>75135</v>
+        <v>75138</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         <v>126600528</v>
       </c>
       <c r="B50" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>126600482</v>
       </c>
       <c r="B51" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         <v>126600470</v>
       </c>
       <c r="B53" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>126600474</v>
       </c>
       <c r="B54" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5866,10 +5866,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126600480</v>
+        <v>126600532</v>
       </c>
       <c r="B55" t="n">
-        <v>79011</v>
+        <v>57657</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5877,34 +5877,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Öjvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>407893</v>
+        <v>408545</v>
       </c>
       <c r="R55" t="n">
-        <v>6857487</v>
+        <v>6857481</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5963,10 +5968,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126600532</v>
+        <v>126600480</v>
       </c>
       <c r="B56" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5974,39 +5979,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Öjvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>408545</v>
+        <v>407893</v>
       </c>
       <c r="R56" t="n">
-        <v>6857481</v>
+        <v>6857487</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6068,7 +6068,7 @@
         <v>126600523</v>
       </c>
       <c r="B57" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
         <v>126600443</v>
       </c>
       <c r="B58" t="n">
-        <v>75135</v>
+        <v>75138</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         <v>126600476</v>
       </c>
       <c r="B59" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         <v>126600436</v>
       </c>
       <c r="B60" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>126600469</v>
       </c>
       <c r="B61" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         <v>126600504</v>
       </c>
       <c r="B62" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>126600510</v>
       </c>
       <c r="B63" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>126600520</v>
       </c>
       <c r="B64" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6849,7 +6849,7 @@
         <v>126600524</v>
       </c>
       <c r="B65" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
         <v>126600466</v>
       </c>
       <c r="B66" t="n">
-        <v>91337</v>
+        <v>91343</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7040,10 +7040,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126600471</v>
+        <v>126600455</v>
       </c>
       <c r="B67" t="n">
-        <v>79011</v>
+        <v>57657</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7051,34 +7051,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Öjvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>408442</v>
+        <v>408538</v>
       </c>
       <c r="R67" t="n">
-        <v>6857466</v>
+        <v>6857478</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7115,7 +7120,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>På björk</t>
+          <t>äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7142,10 +7147,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126600437</v>
+        <v>126600471</v>
       </c>
       <c r="B68" t="n">
-        <v>79629</v>
+        <v>79014</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7153,21 +7158,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7177,10 +7182,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>408172</v>
+        <v>408442</v>
       </c>
       <c r="R68" t="n">
-        <v>6857457</v>
+        <v>6857466</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7213,6 +7218,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7239,10 +7249,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126600472</v>
+        <v>126600437</v>
       </c>
       <c r="B69" t="n">
-        <v>79011</v>
+        <v>79632</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7250,21 +7260,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7274,10 +7284,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>407754</v>
+        <v>408172</v>
       </c>
       <c r="R69" t="n">
-        <v>6857403</v>
+        <v>6857457</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7336,10 +7346,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126600455</v>
+        <v>126600472</v>
       </c>
       <c r="B70" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7347,39 +7357,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Öjvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>408538</v>
+        <v>407754</v>
       </c>
       <c r="R70" t="n">
-        <v>6857478</v>
+        <v>6857403</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7412,11 +7417,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-07-11</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7446,7 +7446,7 @@
         <v>126600440</v>
       </c>
       <c r="B71" t="n">
-        <v>75135</v>
+        <v>75138</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         <v>126600498</v>
       </c>
       <c r="B72" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
         <v>126600492</v>
       </c>
       <c r="B73" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7737,7 +7737,7 @@
         <v>126600503</v>
       </c>
       <c r="B74" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>126600494</v>
       </c>
       <c r="B75" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>126600502</v>
       </c>
       <c r="B76" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8028,7 +8028,7 @@
         <v>126600496</v>
       </c>
       <c r="B77" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         <v>126600493</v>
       </c>
       <c r="B78" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8222,7 +8222,7 @@
         <v>126600491</v>
       </c>
       <c r="B79" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8319,7 +8319,7 @@
         <v>126600442</v>
       </c>
       <c r="B80" t="n">
-        <v>75135</v>
+        <v>75138</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
         <v>126600499</v>
       </c>
       <c r="B82" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8620,7 +8620,7 @@
         <v>126600495</v>
       </c>
       <c r="B83" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 32048-2025 artfynd.xlsx
+++ b/artfynd/A 32048-2025 artfynd.xlsx
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126600452</v>
+        <v>126600530</v>
       </c>
       <c r="B6" t="n">
-        <v>57817</v>
+        <v>79014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>408326</v>
+        <v>407733</v>
       </c>
       <c r="R6" t="n">
-        <v>6857475</v>
+        <v>6857392</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,7 +1165,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126600530</v>
+        <v>126600468</v>
       </c>
       <c r="B7" t="n">
         <v>79014</v>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>407733</v>
+        <v>407930</v>
       </c>
       <c r="R7" t="n">
-        <v>6857392</v>
+        <v>6857464</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1236,6 +1236,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På minst 250 å gammal tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1262,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126600468</v>
+        <v>126600452</v>
       </c>
       <c r="B8" t="n">
-        <v>79014</v>
+        <v>57817</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>407930</v>
+        <v>408326</v>
       </c>
       <c r="R8" t="n">
-        <v>6857464</v>
+        <v>6857475</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1333,11 +1338,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-11</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På minst 250 å gammal tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1364,7 +1364,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126600478</v>
+        <v>126600467</v>
       </c>
       <c r="B9" t="n">
         <v>79014</v>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>407856</v>
+        <v>408188</v>
       </c>
       <c r="R9" t="n">
-        <v>6857458</v>
+        <v>6857426</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1435,6 +1435,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På minst 300 å gammal tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1461,7 +1466,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126600467</v>
+        <v>126600473</v>
       </c>
       <c r="B10" t="n">
         <v>79014</v>
@@ -1496,10 +1501,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>408188</v>
+        <v>407787</v>
       </c>
       <c r="R10" t="n">
-        <v>6857426</v>
+        <v>6857454</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1532,11 +1537,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-11</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På minst 300 å gammal tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1563,7 +1563,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126600486</v>
+        <v>126600515</v>
       </c>
       <c r="B11" t="n">
         <v>79014</v>
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>408464</v>
+        <v>408515</v>
       </c>
       <c r="R11" t="n">
-        <v>6857553</v>
+        <v>6857517</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1660,7 +1660,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126600473</v>
+        <v>126600478</v>
       </c>
       <c r="B12" t="n">
         <v>79014</v>
@@ -1695,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>407787</v>
+        <v>407856</v>
       </c>
       <c r="R12" t="n">
-        <v>6857454</v>
+        <v>6857458</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1757,7 +1757,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126600515</v>
+        <v>126600486</v>
       </c>
       <c r="B13" t="n">
         <v>79014</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>408515</v>
+        <v>408464</v>
       </c>
       <c r="R13" t="n">
-        <v>6857517</v>
+        <v>6857553</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1854,10 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126600434</v>
+        <v>126600519</v>
       </c>
       <c r="B14" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1865,21 +1865,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>408371</v>
+        <v>408462</v>
       </c>
       <c r="R14" t="n">
-        <v>6857511</v>
+        <v>6857472</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1951,7 +1951,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126600519</v>
+        <v>126600481</v>
       </c>
       <c r="B15" t="n">
         <v>79014</v>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>408462</v>
+        <v>407943</v>
       </c>
       <c r="R15" t="n">
-        <v>6857472</v>
+        <v>6857431</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2048,10 +2048,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126600481</v>
+        <v>126600434</v>
       </c>
       <c r="B16" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2059,21 +2059,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2083,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>407943</v>
+        <v>408371</v>
       </c>
       <c r="R16" t="n">
-        <v>6857431</v>
+        <v>6857511</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2533,7 +2533,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126600489</v>
+        <v>126600477</v>
       </c>
       <c r="B21" t="n">
         <v>79014</v>
@@ -2568,10 +2568,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>408527</v>
+        <v>407841</v>
       </c>
       <c r="R21" t="n">
-        <v>6857539</v>
+        <v>6857451</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2630,7 +2630,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126600518</v>
+        <v>126600516</v>
       </c>
       <c r="B22" t="n">
         <v>79014</v>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>408503</v>
+        <v>408508</v>
       </c>
       <c r="R22" t="n">
-        <v>6857520</v>
+        <v>6857524</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2727,7 +2727,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126600477</v>
+        <v>126600489</v>
       </c>
       <c r="B23" t="n">
         <v>79014</v>
@@ -2762,10 +2762,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>407841</v>
+        <v>408527</v>
       </c>
       <c r="R23" t="n">
-        <v>6857451</v>
+        <v>6857539</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2824,7 +2824,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126600516</v>
+        <v>126600518</v>
       </c>
       <c r="B24" t="n">
         <v>79014</v>
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>408508</v>
+        <v>408503</v>
       </c>
       <c r="R24" t="n">
-        <v>6857524</v>
+        <v>6857520</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2921,10 +2921,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126600453</v>
+        <v>126600447</v>
       </c>
       <c r="B25" t="n">
-        <v>57654</v>
+        <v>79603</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2932,39 +2932,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Öjvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>408455</v>
+        <v>408000</v>
       </c>
       <c r="R25" t="n">
-        <v>6857481</v>
+        <v>6857426</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -2997,6 +2992,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>på kulturved</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3217,10 +3217,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126600447</v>
+        <v>126600453</v>
       </c>
       <c r="B28" t="n">
-        <v>79603</v>
+        <v>57654</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3228,34 +3228,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Öjvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>408000</v>
+        <v>408455</v>
       </c>
       <c r="R28" t="n">
-        <v>6857426</v>
+        <v>6857481</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3288,11 +3293,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-07-11</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>på kulturved</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3319,10 +3319,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126600522</v>
+        <v>126600465</v>
       </c>
       <c r="B29" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3330,21 +3330,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3354,10 +3354,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>408161</v>
+        <v>408117</v>
       </c>
       <c r="R29" t="n">
-        <v>6857473</v>
+        <v>6857480</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3416,10 +3416,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126600465</v>
+        <v>126600522</v>
       </c>
       <c r="B30" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3427,21 +3427,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3451,10 +3451,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>408117</v>
+        <v>408161</v>
       </c>
       <c r="R30" t="n">
-        <v>6857480</v>
+        <v>6857473</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3998,10 +3998,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126600517</v>
+        <v>126600445</v>
       </c>
       <c r="B36" t="n">
-        <v>79014</v>
+        <v>75138</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4009,21 +4009,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4033,10 +4033,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>408506</v>
+        <v>407749</v>
       </c>
       <c r="R36" t="n">
-        <v>6857522</v>
+        <v>6857376</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4095,7 +4095,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126600514</v>
+        <v>126600517</v>
       </c>
       <c r="B37" t="n">
         <v>79014</v>
@@ -4130,10 +4130,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>408519</v>
+        <v>408506</v>
       </c>
       <c r="R37" t="n">
-        <v>6857527</v>
+        <v>6857522</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4192,7 +4192,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126600531</v>
+        <v>126600514</v>
       </c>
       <c r="B38" t="n">
         <v>79014</v>
@@ -4227,10 +4227,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>407732</v>
+        <v>408519</v>
       </c>
       <c r="R38" t="n">
-        <v>6857407</v>
+        <v>6857527</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4289,7 +4289,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126600505</v>
+        <v>126600531</v>
       </c>
       <c r="B39" t="n">
         <v>79014</v>
@@ -4324,10 +4324,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>408526</v>
+        <v>407732</v>
       </c>
       <c r="R39" t="n">
-        <v>6857470</v>
+        <v>6857407</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4386,10 +4386,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126600445</v>
+        <v>126600505</v>
       </c>
       <c r="B40" t="n">
-        <v>75138</v>
+        <v>79014</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4397,21 +4397,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4421,10 +4421,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>407749</v>
+        <v>408526</v>
       </c>
       <c r="R40" t="n">
-        <v>6857376</v>
+        <v>6857470</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4483,10 +4483,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126600484</v>
+        <v>126600533</v>
       </c>
       <c r="B41" t="n">
-        <v>79014</v>
+        <v>88728</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4494,21 +4494,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4518,13 +4518,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>408137</v>
+        <v>408505</v>
       </c>
       <c r="R41" t="n">
-        <v>6857510</v>
+        <v>6857526</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4580,7 +4580,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126600527</v>
+        <v>126600484</v>
       </c>
       <c r="B42" t="n">
         <v>79014</v>
@@ -4615,10 +4615,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>407828</v>
+        <v>408137</v>
       </c>
       <c r="R42" t="n">
-        <v>6857402</v>
+        <v>6857510</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4677,7 +4677,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126600525</v>
+        <v>126600527</v>
       </c>
       <c r="B43" t="n">
         <v>79014</v>
@@ -4712,10 +4712,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>407847</v>
+        <v>407828</v>
       </c>
       <c r="R43" t="n">
-        <v>6857413</v>
+        <v>6857402</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4774,10 +4774,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126600533</v>
+        <v>126600525</v>
       </c>
       <c r="B44" t="n">
-        <v>88728</v>
+        <v>79014</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4785,21 +4785,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4809,13 +4809,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>408505</v>
+        <v>407847</v>
       </c>
       <c r="R44" t="n">
-        <v>6857526</v>
+        <v>6857413</v>
       </c>
       <c r="S44" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4871,50 +4871,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126600451</v>
+        <v>126600439</v>
       </c>
       <c r="B45" t="n">
-        <v>56849</v>
+        <v>75138</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100138</v>
+        <v>6440</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Öjvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>408398</v>
+        <v>408539</v>
       </c>
       <c r="R45" t="n">
-        <v>6857453</v>
+        <v>6857475</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4947,6 +4942,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>rikligt, på minst 300 år gammal gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -4973,10 +4973,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126600439</v>
+        <v>126600438</v>
       </c>
       <c r="B46" t="n">
-        <v>75138</v>
+        <v>79632</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4984,21 +4984,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5008,10 +5008,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>408539</v>
+        <v>408116</v>
       </c>
       <c r="R46" t="n">
-        <v>6857475</v>
+        <v>6857480</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5044,11 +5044,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-07-11</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>rikligt, på minst 300 år gammal gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5075,10 +5070,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126600438</v>
+        <v>126600508</v>
       </c>
       <c r="B47" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5086,21 +5081,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5110,10 +5105,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>408116</v>
+        <v>408528</v>
       </c>
       <c r="R47" t="n">
-        <v>6857480</v>
+        <v>6857478</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5172,45 +5167,50 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126600508</v>
+        <v>126600451</v>
       </c>
       <c r="B48" t="n">
-        <v>79014</v>
+        <v>56849</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Öjvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>408528</v>
+        <v>408398</v>
       </c>
       <c r="R48" t="n">
-        <v>6857478</v>
+        <v>6857453</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5866,10 +5866,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126600532</v>
+        <v>126600480</v>
       </c>
       <c r="B55" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5877,39 +5877,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Öjvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>408545</v>
+        <v>407893</v>
       </c>
       <c r="R55" t="n">
-        <v>6857481</v>
+        <v>6857487</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5968,10 +5963,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126600480</v>
+        <v>126600532</v>
       </c>
       <c r="B56" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5979,34 +5974,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Öjvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>407893</v>
+        <v>408545</v>
       </c>
       <c r="R56" t="n">
-        <v>6857487</v>
+        <v>6857481</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6065,10 +6065,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126600523</v>
+        <v>126600443</v>
       </c>
       <c r="B57" t="n">
-        <v>79014</v>
+        <v>75138</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6076,21 +6076,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6100,10 +6100,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>407896</v>
+        <v>408515</v>
       </c>
       <c r="R57" t="n">
-        <v>6857412</v>
+        <v>6857485</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6162,10 +6162,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126600443</v>
+        <v>126600436</v>
       </c>
       <c r="B58" t="n">
-        <v>75138</v>
+        <v>79632</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6173,21 +6173,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6197,10 +6197,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>408515</v>
+        <v>408460</v>
       </c>
       <c r="R58" t="n">
-        <v>6857485</v>
+        <v>6857480</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6259,7 +6259,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126600476</v>
+        <v>126600523</v>
       </c>
       <c r="B59" t="n">
         <v>79014</v>
@@ -6294,10 +6294,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>407830</v>
+        <v>407896</v>
       </c>
       <c r="R59" t="n">
-        <v>6857446</v>
+        <v>6857412</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6356,10 +6356,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126600436</v>
+        <v>126600476</v>
       </c>
       <c r="B60" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6367,21 +6367,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6391,10 +6391,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>408460</v>
+        <v>407830</v>
       </c>
       <c r="R60" t="n">
-        <v>6857480</v>
+        <v>6857446</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6453,7 +6453,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126600469</v>
+        <v>126600524</v>
       </c>
       <c r="B61" t="n">
         <v>79014</v>
@@ -6488,10 +6488,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>408448</v>
+        <v>407853</v>
       </c>
       <c r="R61" t="n">
-        <v>6857547</v>
+        <v>6857393</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6524,11 +6524,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-07-11</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>På minst 250 å gammal tall</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6555,7 +6550,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126600504</v>
+        <v>126600469</v>
       </c>
       <c r="B62" t="n">
         <v>79014</v>
@@ -6590,10 +6585,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>408547</v>
+        <v>408448</v>
       </c>
       <c r="R62" t="n">
-        <v>6857475</v>
+        <v>6857547</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6626,6 +6621,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>På minst 250 å gammal tall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6652,7 +6652,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126600510</v>
+        <v>126600504</v>
       </c>
       <c r="B63" t="n">
         <v>79014</v>
@@ -6687,10 +6687,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>408517</v>
+        <v>408547</v>
       </c>
       <c r="R63" t="n">
-        <v>6857489</v>
+        <v>6857475</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6749,7 +6749,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126600520</v>
+        <v>126600510</v>
       </c>
       <c r="B64" t="n">
         <v>79014</v>
@@ -6784,10 +6784,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>408455</v>
+        <v>408517</v>
       </c>
       <c r="R64" t="n">
-        <v>6857481</v>
+        <v>6857489</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6846,7 +6846,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126600524</v>
+        <v>126600520</v>
       </c>
       <c r="B65" t="n">
         <v>79014</v>
@@ -6881,10 +6881,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>407853</v>
+        <v>408455</v>
       </c>
       <c r="R65" t="n">
-        <v>6857393</v>
+        <v>6857481</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7040,10 +7040,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126600455</v>
+        <v>126600437</v>
       </c>
       <c r="B67" t="n">
-        <v>57657</v>
+        <v>79632</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7051,39 +7051,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Öjvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>408538</v>
+        <v>408172</v>
       </c>
       <c r="R67" t="n">
-        <v>6857478</v>
+        <v>6857457</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7116,11 +7111,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-07-11</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7147,10 +7137,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126600471</v>
+        <v>126600455</v>
       </c>
       <c r="B68" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7158,34 +7148,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Öjvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>408442</v>
+        <v>408538</v>
       </c>
       <c r="R68" t="n">
-        <v>6857466</v>
+        <v>6857478</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7222,7 +7217,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>På björk</t>
+          <t>äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7249,10 +7244,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126600437</v>
+        <v>126600471</v>
       </c>
       <c r="B69" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7260,21 +7255,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7284,10 +7279,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>408172</v>
+        <v>408442</v>
       </c>
       <c r="R69" t="n">
-        <v>6857457</v>
+        <v>6857466</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7320,6 +7315,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8219,10 +8219,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126600491</v>
+        <v>126600442</v>
       </c>
       <c r="B79" t="n">
-        <v>79014</v>
+        <v>75138</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8230,21 +8230,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8254,10 +8254,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>408554</v>
+        <v>408565</v>
       </c>
       <c r="R79" t="n">
-        <v>6857516</v>
+        <v>6857470</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8316,10 +8316,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126600442</v>
+        <v>126600491</v>
       </c>
       <c r="B80" t="n">
-        <v>75138</v>
+        <v>79014</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8327,21 +8327,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8351,10 +8351,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>408565</v>
+        <v>408554</v>
       </c>
       <c r="R80" t="n">
-        <v>6857470</v>
+        <v>6857516</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>

--- a/artfynd/A 32048-2025 artfynd.xlsx
+++ b/artfynd/A 32048-2025 artfynd.xlsx
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126600530</v>
+        <v>126600452</v>
       </c>
       <c r="B6" t="n">
-        <v>79014</v>
+        <v>57817</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>407733</v>
+        <v>408326</v>
       </c>
       <c r="R6" t="n">
-        <v>6857392</v>
+        <v>6857475</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,7 +1165,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126600468</v>
+        <v>126600530</v>
       </c>
       <c r="B7" t="n">
         <v>79014</v>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>407930</v>
+        <v>407733</v>
       </c>
       <c r="R7" t="n">
-        <v>6857464</v>
+        <v>6857392</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1236,11 +1236,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-11</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På minst 250 å gammal tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1267,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126600452</v>
+        <v>126600468</v>
       </c>
       <c r="B8" t="n">
-        <v>57817</v>
+        <v>79014</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>408326</v>
+        <v>407930</v>
       </c>
       <c r="R8" t="n">
-        <v>6857475</v>
+        <v>6857464</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1338,6 +1333,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På minst 250 å gammal tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1364,7 +1364,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126600467</v>
+        <v>126600478</v>
       </c>
       <c r="B9" t="n">
         <v>79014</v>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>408188</v>
+        <v>407856</v>
       </c>
       <c r="R9" t="n">
-        <v>6857426</v>
+        <v>6857458</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1435,11 +1435,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-07-11</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På minst 300 å gammal tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1466,7 +1461,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126600473</v>
+        <v>126600486</v>
       </c>
       <c r="B10" t="n">
         <v>79014</v>
@@ -1501,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>407787</v>
+        <v>408464</v>
       </c>
       <c r="R10" t="n">
-        <v>6857454</v>
+        <v>6857553</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1563,7 +1558,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126600515</v>
+        <v>126600467</v>
       </c>
       <c r="B11" t="n">
         <v>79014</v>
@@ -1598,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>408515</v>
+        <v>408188</v>
       </c>
       <c r="R11" t="n">
-        <v>6857517</v>
+        <v>6857426</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1634,6 +1629,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På minst 300 å gammal tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1660,7 +1660,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126600478</v>
+        <v>126600473</v>
       </c>
       <c r="B12" t="n">
         <v>79014</v>
@@ -1695,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>407856</v>
+        <v>407787</v>
       </c>
       <c r="R12" t="n">
-        <v>6857458</v>
+        <v>6857454</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1757,7 +1757,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126600486</v>
+        <v>126600515</v>
       </c>
       <c r="B13" t="n">
         <v>79014</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>408464</v>
+        <v>408515</v>
       </c>
       <c r="R13" t="n">
-        <v>6857553</v>
+        <v>6857517</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2145,10 +2145,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126600521</v>
+        <v>126600441</v>
       </c>
       <c r="B17" t="n">
-        <v>79014</v>
+        <v>75138</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2156,21 +2156,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>408449</v>
+        <v>408546</v>
       </c>
       <c r="R17" t="n">
-        <v>6857472</v>
+        <v>6857483</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2242,7 +2242,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126600509</v>
+        <v>126600521</v>
       </c>
       <c r="B18" t="n">
         <v>79014</v>
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>408514</v>
+        <v>408449</v>
       </c>
       <c r="R18" t="n">
-        <v>6857480</v>
+        <v>6857472</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2339,7 +2339,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126600512</v>
+        <v>126600509</v>
       </c>
       <c r="B19" t="n">
         <v>79014</v>
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>408523</v>
+        <v>408514</v>
       </c>
       <c r="R19" t="n">
-        <v>6857511</v>
+        <v>6857480</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2436,10 +2436,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126600441</v>
+        <v>126600512</v>
       </c>
       <c r="B20" t="n">
-        <v>75138</v>
+        <v>79014</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2447,21 +2447,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>408546</v>
+        <v>408523</v>
       </c>
       <c r="R20" t="n">
-        <v>6857483</v>
+        <v>6857511</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3319,10 +3319,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126600465</v>
+        <v>126600522</v>
       </c>
       <c r="B29" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3330,21 +3330,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3354,10 +3354,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>408117</v>
+        <v>408161</v>
       </c>
       <c r="R29" t="n">
-        <v>6857480</v>
+        <v>6857473</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3416,10 +3416,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126600522</v>
+        <v>126600465</v>
       </c>
       <c r="B30" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3427,21 +3427,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3451,10 +3451,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>408161</v>
+        <v>408117</v>
       </c>
       <c r="R30" t="n">
-        <v>6857473</v>
+        <v>6857480</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -5070,45 +5070,50 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126600508</v>
+        <v>126600451</v>
       </c>
       <c r="B47" t="n">
-        <v>79014</v>
+        <v>56849</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Öjvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>408528</v>
+        <v>408398</v>
       </c>
       <c r="R47" t="n">
-        <v>6857478</v>
+        <v>6857453</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5167,50 +5172,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126600451</v>
+        <v>126600508</v>
       </c>
       <c r="B48" t="n">
-        <v>56849</v>
+        <v>79014</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Öjvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>408398</v>
+        <v>408528</v>
       </c>
       <c r="R48" t="n">
-        <v>6857453</v>
+        <v>6857478</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>

--- a/artfynd/A 32048-2025 artfynd.xlsx
+++ b/artfynd/A 32048-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126600435</v>
       </c>
       <c r="B2" t="n">
-        <v>79632</v>
+        <v>79629</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126600529</v>
       </c>
       <c r="B3" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>126600490</v>
       </c>
       <c r="B5" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126600452</v>
+        <v>126600530</v>
       </c>
       <c r="B6" t="n">
-        <v>57817</v>
+        <v>79011</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>408326</v>
+        <v>407733</v>
       </c>
       <c r="R6" t="n">
-        <v>6857475</v>
+        <v>6857392</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126600530</v>
+        <v>126600468</v>
       </c>
       <c r="B7" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>407733</v>
+        <v>407930</v>
       </c>
       <c r="R7" t="n">
-        <v>6857392</v>
+        <v>6857464</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1236,6 +1236,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På minst 250 å gammal tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1262,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126600468</v>
+        <v>126600452</v>
       </c>
       <c r="B8" t="n">
-        <v>79014</v>
+        <v>57817</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>407930</v>
+        <v>408326</v>
       </c>
       <c r="R8" t="n">
-        <v>6857464</v>
+        <v>6857475</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1333,11 +1338,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-11</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På minst 250 å gammal tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1367,7 +1367,7 @@
         <v>126600478</v>
       </c>
       <c r="B9" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126600486</v>
+        <v>126600467</v>
       </c>
       <c r="B10" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>408464</v>
+        <v>408188</v>
       </c>
       <c r="R10" t="n">
-        <v>6857553</v>
+        <v>6857426</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1532,6 +1532,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På minst 300 å gammal tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1558,10 +1563,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126600467</v>
+        <v>126600486</v>
       </c>
       <c r="B11" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1593,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>408188</v>
+        <v>408464</v>
       </c>
       <c r="R11" t="n">
-        <v>6857426</v>
+        <v>6857553</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1629,11 +1634,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-11</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På minst 300 å gammal tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1663,7 +1663,7 @@
         <v>126600473</v>
       </c>
       <c r="B12" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>126600515</v>
       </c>
       <c r="B13" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1854,10 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126600519</v>
+        <v>126600434</v>
       </c>
       <c r="B14" t="n">
-        <v>79014</v>
+        <v>79629</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1865,21 +1865,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>408462</v>
+        <v>408371</v>
       </c>
       <c r="R14" t="n">
-        <v>6857472</v>
+        <v>6857511</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126600481</v>
+        <v>126600519</v>
       </c>
       <c r="B15" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>407943</v>
+        <v>408462</v>
       </c>
       <c r="R15" t="n">
-        <v>6857431</v>
+        <v>6857472</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2048,10 +2048,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126600434</v>
+        <v>126600481</v>
       </c>
       <c r="B16" t="n">
-        <v>79632</v>
+        <v>79011</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2059,21 +2059,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2083,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>408371</v>
+        <v>407943</v>
       </c>
       <c r="R16" t="n">
-        <v>6857511</v>
+        <v>6857431</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2145,10 +2145,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126600441</v>
+        <v>126600521</v>
       </c>
       <c r="B17" t="n">
-        <v>75138</v>
+        <v>79011</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2156,21 +2156,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>408546</v>
+        <v>408449</v>
       </c>
       <c r="R17" t="n">
-        <v>6857483</v>
+        <v>6857472</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2242,10 +2242,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126600521</v>
+        <v>126600509</v>
       </c>
       <c r="B18" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>408449</v>
+        <v>408514</v>
       </c>
       <c r="R18" t="n">
-        <v>6857472</v>
+        <v>6857480</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2339,10 +2339,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126600509</v>
+        <v>126600512</v>
       </c>
       <c r="B19" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>408514</v>
+        <v>408523</v>
       </c>
       <c r="R19" t="n">
-        <v>6857480</v>
+        <v>6857511</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2436,10 +2436,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126600512</v>
+        <v>126600441</v>
       </c>
       <c r="B20" t="n">
-        <v>79014</v>
+        <v>75135</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2447,21 +2447,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>408523</v>
+        <v>408546</v>
       </c>
       <c r="R20" t="n">
-        <v>6857511</v>
+        <v>6857483</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2533,10 +2533,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126600477</v>
+        <v>126600489</v>
       </c>
       <c r="B21" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2568,10 +2568,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>407841</v>
+        <v>408527</v>
       </c>
       <c r="R21" t="n">
-        <v>6857451</v>
+        <v>6857539</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2630,10 +2630,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126600516</v>
+        <v>126600518</v>
       </c>
       <c r="B22" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>408508</v>
+        <v>408503</v>
       </c>
       <c r="R22" t="n">
-        <v>6857524</v>
+        <v>6857520</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2727,10 +2727,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126600489</v>
+        <v>126600477</v>
       </c>
       <c r="B23" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2762,10 +2762,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>408527</v>
+        <v>407841</v>
       </c>
       <c r="R23" t="n">
-        <v>6857539</v>
+        <v>6857451</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2824,10 +2824,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126600518</v>
+        <v>126600516</v>
       </c>
       <c r="B24" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>408503</v>
+        <v>408508</v>
       </c>
       <c r="R24" t="n">
-        <v>6857520</v>
+        <v>6857524</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2921,10 +2921,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126600447</v>
+        <v>126600507</v>
       </c>
       <c r="B25" t="n">
-        <v>79603</v>
+        <v>79011</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2932,21 +2932,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2956,10 +2956,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>408000</v>
+        <v>408520</v>
       </c>
       <c r="R25" t="n">
-        <v>6857426</v>
+        <v>6857470</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -2992,11 +2992,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-11</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>på kulturved</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3023,10 +3018,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126600507</v>
+        <v>126600487</v>
       </c>
       <c r="B26" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3058,10 +3053,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>408520</v>
+        <v>408513</v>
       </c>
       <c r="R26" t="n">
-        <v>6857470</v>
+        <v>6857559</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3120,10 +3115,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126600487</v>
+        <v>126600453</v>
       </c>
       <c r="B27" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3131,34 +3126,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Öjvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>408513</v>
+        <v>408455</v>
       </c>
       <c r="R27" t="n">
-        <v>6857559</v>
+        <v>6857481</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3217,10 +3217,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126600453</v>
+        <v>126600447</v>
       </c>
       <c r="B28" t="n">
-        <v>57654</v>
+        <v>79600</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3228,39 +3228,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Öjvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>408455</v>
+        <v>408000</v>
       </c>
       <c r="R28" t="n">
-        <v>6857481</v>
+        <v>6857426</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3293,6 +3288,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>på kulturved</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3319,10 +3319,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126600522</v>
+        <v>126600465</v>
       </c>
       <c r="B29" t="n">
-        <v>79014</v>
+        <v>78770</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3330,21 +3330,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3354,10 +3354,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>408161</v>
+        <v>408117</v>
       </c>
       <c r="R29" t="n">
-        <v>6857473</v>
+        <v>6857480</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3416,10 +3416,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126600465</v>
+        <v>126600522</v>
       </c>
       <c r="B30" t="n">
-        <v>78773</v>
+        <v>79011</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3427,21 +3427,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3451,10 +3451,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>408117</v>
+        <v>408161</v>
       </c>
       <c r="R30" t="n">
-        <v>6857480</v>
+        <v>6857473</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3516,7 +3516,7 @@
         <v>126600475</v>
       </c>
       <c r="B31" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3613,7 +3613,7 @@
         <v>126600511</v>
       </c>
       <c r="B32" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         <v>126600488</v>
       </c>
       <c r="B33" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>126600483</v>
       </c>
       <c r="B34" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>126600485</v>
       </c>
       <c r="B35" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3998,10 +3998,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126600445</v>
+        <v>126600517</v>
       </c>
       <c r="B36" t="n">
-        <v>75138</v>
+        <v>79011</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4009,21 +4009,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4033,10 +4033,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>407749</v>
+        <v>408506</v>
       </c>
       <c r="R36" t="n">
-        <v>6857376</v>
+        <v>6857522</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4095,10 +4095,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126600517</v>
+        <v>126600514</v>
       </c>
       <c r="B37" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4130,10 +4130,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>408506</v>
+        <v>408519</v>
       </c>
       <c r="R37" t="n">
-        <v>6857522</v>
+        <v>6857527</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4192,10 +4192,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126600514</v>
+        <v>126600531</v>
       </c>
       <c r="B38" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4227,10 +4227,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>408519</v>
+        <v>407732</v>
       </c>
       <c r="R38" t="n">
-        <v>6857527</v>
+        <v>6857407</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4289,10 +4289,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126600531</v>
+        <v>126600505</v>
       </c>
       <c r="B39" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4324,10 +4324,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>407732</v>
+        <v>408526</v>
       </c>
       <c r="R39" t="n">
-        <v>6857407</v>
+        <v>6857470</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4386,10 +4386,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126600505</v>
+        <v>126600445</v>
       </c>
       <c r="B40" t="n">
-        <v>79014</v>
+        <v>75135</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4397,21 +4397,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4421,10 +4421,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>408526</v>
+        <v>407749</v>
       </c>
       <c r="R40" t="n">
-        <v>6857470</v>
+        <v>6857376</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4483,10 +4483,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126600533</v>
+        <v>126600484</v>
       </c>
       <c r="B41" t="n">
-        <v>88728</v>
+        <v>79011</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4494,21 +4494,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4518,13 +4518,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>408505</v>
+        <v>408137</v>
       </c>
       <c r="R41" t="n">
-        <v>6857526</v>
+        <v>6857510</v>
       </c>
       <c r="S41" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4580,10 +4580,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126600484</v>
+        <v>126600527</v>
       </c>
       <c r="B42" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4615,10 +4615,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>408137</v>
+        <v>407828</v>
       </c>
       <c r="R42" t="n">
-        <v>6857510</v>
+        <v>6857402</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4677,10 +4677,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126600527</v>
+        <v>126600525</v>
       </c>
       <c r="B43" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4712,10 +4712,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>407828</v>
+        <v>407847</v>
       </c>
       <c r="R43" t="n">
-        <v>6857402</v>
+        <v>6857413</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4774,10 +4774,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126600525</v>
+        <v>126600533</v>
       </c>
       <c r="B44" t="n">
-        <v>79014</v>
+        <v>88722</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4785,21 +4785,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4809,13 +4809,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>407847</v>
+        <v>408505</v>
       </c>
       <c r="R44" t="n">
-        <v>6857413</v>
+        <v>6857526</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4871,45 +4871,50 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126600439</v>
+        <v>126600451</v>
       </c>
       <c r="B45" t="n">
-        <v>75138</v>
+        <v>56849</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6440</v>
+        <v>100138</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Öjvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>408539</v>
+        <v>408398</v>
       </c>
       <c r="R45" t="n">
-        <v>6857475</v>
+        <v>6857453</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4942,11 +4947,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-07-11</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>rikligt, på minst 300 år gammal gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -4973,10 +4973,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126600438</v>
+        <v>126600439</v>
       </c>
       <c r="B46" t="n">
-        <v>79632</v>
+        <v>75135</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4984,21 +4984,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5008,10 +5008,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>408116</v>
+        <v>408539</v>
       </c>
       <c r="R46" t="n">
-        <v>6857480</v>
+        <v>6857475</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5044,6 +5044,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>rikligt, på minst 300 år gammal gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5070,50 +5075,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126600451</v>
+        <v>126600438</v>
       </c>
       <c r="B47" t="n">
-        <v>56849</v>
+        <v>79629</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Öjvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>408398</v>
+        <v>408116</v>
       </c>
       <c r="R47" t="n">
-        <v>6857453</v>
+        <v>6857480</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5175,7 +5175,7 @@
         <v>126600508</v>
       </c>
       <c r="B48" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>126600444</v>
       </c>
       <c r="B49" t="n">
-        <v>75138</v>
+        <v>75135</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         <v>126600528</v>
       </c>
       <c r="B50" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>126600482</v>
       </c>
       <c r="B51" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         <v>126600470</v>
       </c>
       <c r="B53" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>126600474</v>
       </c>
       <c r="B54" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         <v>126600480</v>
       </c>
       <c r="B55" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6065,10 +6065,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126600443</v>
+        <v>126600523</v>
       </c>
       <c r="B57" t="n">
-        <v>75138</v>
+        <v>79011</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6076,21 +6076,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6100,10 +6100,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>408515</v>
+        <v>407896</v>
       </c>
       <c r="R57" t="n">
-        <v>6857485</v>
+        <v>6857412</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6162,10 +6162,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126600436</v>
+        <v>126600443</v>
       </c>
       <c r="B58" t="n">
-        <v>79632</v>
+        <v>75135</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6173,21 +6173,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6197,10 +6197,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>408460</v>
+        <v>408515</v>
       </c>
       <c r="R58" t="n">
-        <v>6857480</v>
+        <v>6857485</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6259,10 +6259,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126600523</v>
+        <v>126600476</v>
       </c>
       <c r="B59" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6294,10 +6294,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>407896</v>
+        <v>407830</v>
       </c>
       <c r="R59" t="n">
-        <v>6857412</v>
+        <v>6857446</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6356,10 +6356,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126600476</v>
+        <v>126600436</v>
       </c>
       <c r="B60" t="n">
-        <v>79014</v>
+        <v>79629</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6367,21 +6367,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6391,10 +6391,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>407830</v>
+        <v>408460</v>
       </c>
       <c r="R60" t="n">
-        <v>6857446</v>
+        <v>6857480</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6453,10 +6453,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126600524</v>
+        <v>126600469</v>
       </c>
       <c r="B61" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6488,10 +6488,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>407853</v>
+        <v>408448</v>
       </c>
       <c r="R61" t="n">
-        <v>6857393</v>
+        <v>6857547</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6524,6 +6524,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>På minst 250 å gammal tall</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6550,10 +6555,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126600469</v>
+        <v>126600504</v>
       </c>
       <c r="B62" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6585,10 +6590,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>408448</v>
+        <v>408547</v>
       </c>
       <c r="R62" t="n">
-        <v>6857547</v>
+        <v>6857475</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6621,11 +6626,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-07-11</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>På minst 250 å gammal tall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6652,10 +6652,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126600504</v>
+        <v>126600510</v>
       </c>
       <c r="B63" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6687,10 +6687,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>408547</v>
+        <v>408517</v>
       </c>
       <c r="R63" t="n">
-        <v>6857475</v>
+        <v>6857489</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6749,10 +6749,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126600510</v>
+        <v>126600520</v>
       </c>
       <c r="B64" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6784,10 +6784,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>408517</v>
+        <v>408455</v>
       </c>
       <c r="R64" t="n">
-        <v>6857489</v>
+        <v>6857481</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6846,10 +6846,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126600520</v>
+        <v>126600524</v>
       </c>
       <c r="B65" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6881,10 +6881,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>408455</v>
+        <v>407853</v>
       </c>
       <c r="R65" t="n">
-        <v>6857481</v>
+        <v>6857393</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6946,7 +6946,7 @@
         <v>126600466</v>
       </c>
       <c r="B66" t="n">
-        <v>91343</v>
+        <v>91337</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7040,10 +7040,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126600437</v>
+        <v>126600471</v>
       </c>
       <c r="B67" t="n">
-        <v>79632</v>
+        <v>79011</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7051,21 +7051,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7075,10 +7075,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>408172</v>
+        <v>408442</v>
       </c>
       <c r="R67" t="n">
-        <v>6857457</v>
+        <v>6857466</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7111,6 +7111,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7137,10 +7142,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126600455</v>
+        <v>126600437</v>
       </c>
       <c r="B68" t="n">
-        <v>57657</v>
+        <v>79629</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7148,39 +7153,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Öjvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>408538</v>
+        <v>408172</v>
       </c>
       <c r="R68" t="n">
-        <v>6857478</v>
+        <v>6857457</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7213,11 +7213,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-07-11</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7244,10 +7239,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126600471</v>
+        <v>126600472</v>
       </c>
       <c r="B69" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7279,10 +7274,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>408442</v>
+        <v>407754</v>
       </c>
       <c r="R69" t="n">
-        <v>6857466</v>
+        <v>6857403</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7315,11 +7310,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-07-11</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7346,10 +7336,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126600472</v>
+        <v>126600455</v>
       </c>
       <c r="B70" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7357,34 +7347,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Öjvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>407754</v>
+        <v>408538</v>
       </c>
       <c r="R70" t="n">
-        <v>6857403</v>
+        <v>6857478</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7417,6 +7412,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7446,7 +7446,7 @@
         <v>126600440</v>
       </c>
       <c r="B71" t="n">
-        <v>75138</v>
+        <v>75135</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         <v>126600498</v>
       </c>
       <c r="B72" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
         <v>126600492</v>
       </c>
       <c r="B73" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7737,7 +7737,7 @@
         <v>126600503</v>
       </c>
       <c r="B74" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>126600494</v>
       </c>
       <c r="B75" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>126600502</v>
       </c>
       <c r="B76" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8028,7 +8028,7 @@
         <v>126600496</v>
       </c>
       <c r="B77" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         <v>126600493</v>
       </c>
       <c r="B78" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8219,10 +8219,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126600442</v>
+        <v>126600491</v>
       </c>
       <c r="B79" t="n">
-        <v>75138</v>
+        <v>79011</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8230,21 +8230,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8254,10 +8254,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>408565</v>
+        <v>408554</v>
       </c>
       <c r="R79" t="n">
-        <v>6857470</v>
+        <v>6857516</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8316,10 +8316,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126600491</v>
+        <v>126600442</v>
       </c>
       <c r="B80" t="n">
-        <v>79014</v>
+        <v>75135</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8327,21 +8327,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8351,10 +8351,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>408554</v>
+        <v>408565</v>
       </c>
       <c r="R80" t="n">
-        <v>6857516</v>
+        <v>6857470</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8523,7 +8523,7 @@
         <v>126600499</v>
       </c>
       <c r="B82" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8620,7 +8620,7 @@
         <v>126600495</v>
       </c>
       <c r="B83" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 32048-2025 artfynd.xlsx
+++ b/artfynd/A 32048-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY84"/>
+  <dimension ref="A1:AZ84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600533</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600467</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600468</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600469</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600470</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1279,6 +1309,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600471</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1376,6 +1411,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600472</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1473,6 +1513,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600473</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1570,6 +1615,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600474</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1667,6 +1717,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600475</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1764,6 +1819,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600476</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1861,6 +1921,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600477</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1958,6 +2023,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600478</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2055,6 +2125,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600480</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2152,6 +2227,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600481</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2249,6 +2329,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600482</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2346,6 +2431,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600483</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2443,6 +2533,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600484</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2540,6 +2635,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600485</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2637,6 +2737,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600486</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2734,6 +2839,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600487</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2831,6 +2941,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600488</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2928,6 +3043,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600489</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3025,6 +3145,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600490</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3122,6 +3247,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600491</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3219,6 +3349,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600492</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3316,6 +3451,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600493</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3413,6 +3553,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600494</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3510,6 +3655,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600495</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3607,6 +3757,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600496</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3704,6 +3859,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600498</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3801,6 +3961,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600499</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3898,6 +4063,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600500</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3995,6 +4165,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600502</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4092,6 +4267,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600503</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4189,6 +4369,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600504</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4286,6 +4471,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600505</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4383,6 +4573,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600507</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4480,6 +4675,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600508</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4577,6 +4777,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600509</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4674,6 +4879,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600510</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4771,6 +4981,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600511</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4868,6 +5083,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600512</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4965,6 +5185,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600514</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5062,6 +5287,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600515</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5159,6 +5389,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600516</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5256,6 +5491,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600517</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5353,6 +5593,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600518</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5450,6 +5695,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600519</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5547,6 +5797,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600520</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5644,6 +5899,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600521</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5741,6 +6001,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600522</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5838,6 +6103,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600523</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5935,6 +6205,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600524</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6032,6 +6307,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600525</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6129,6 +6409,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600527</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6226,6 +6511,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600528</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6323,6 +6613,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600529</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6420,6 +6715,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600530</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6517,6 +6817,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600531</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6619,6 +6924,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600439</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6716,6 +7026,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600440</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6813,6 +7128,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600441</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6910,6 +7230,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600442</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7007,6 +7332,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600443</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7104,6 +7434,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600444</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7201,6 +7536,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600445</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7298,6 +7638,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600434</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7395,6 +7740,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600435</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7492,6 +7842,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600436</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7589,6 +7944,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600437</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7686,6 +8046,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600438</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7788,6 +8153,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600453</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7895,6 +8265,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600454</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8002,6 +8377,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600455</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8109,6 +8489,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600457</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8211,6 +8596,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600532</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8313,6 +8703,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600450</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8415,6 +8810,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600451</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8512,6 +8912,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600452</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8609,6 +9014,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600465</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8711,6 +9121,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600447</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8808,8 +9223,98 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600449</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>